--- a/evaluation_output/per_landmark_results.xlsx
+++ b/evaluation_output/per_landmark_results.xlsx
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.576</v>
+        <v>2.14</v>
       </c>
       <c r="C4" t="n">
-        <v>2.714</v>
+        <v>3.05</v>
       </c>
       <c r="D4" t="n">
-        <v>62.4</v>
+        <v>73</v>
       </c>
       <c r="E4" t="n">
-        <v>83.7</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="5">
